--- a/docs/story-packs/orders-search-progression.xlsx
+++ b/docs/story-packs/orders-search-progression.xlsx
@@ -872,7 +872,7 @@
       </c>
       <c r="E4" s="14" t="inlineStr">
         <is>
-          <t>G2O TECH SOLUTIONS, Bastrop, LA, US</t>
+          <t>BASTROP TERMINAL, Bastrop, LA, US</t>
         </is>
       </c>
       <c r="F4" s="15" t="inlineStr">
@@ -914,7 +914,7 @@
       </c>
       <c r="E5" s="14" t="inlineStr">
         <is>
-          <t>SOLVAY CHEMICALS PL, Green River, WY, US</t>
+          <t>GREEN RIVER TERMINAL, Green River, WY, US</t>
         </is>
       </c>
       <c r="F5" s="15" t="inlineStr">
